--- a/outputs/279-23.xlsx
+++ b/outputs/279-23.xlsx
@@ -101,8 +101,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -298,166 +302,166 @@
   <dimension ref="A3:B26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.29"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>0</v>
       </c>
     </row>

--- a/outputs/279-23.xlsx
+++ b/outputs/279-23.xlsx
@@ -1,62 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57C3BF7-5E55-43A4-9FB5-4DA9C7149696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B2CBF329-73BD-49A3-8AB2-0F20F4C378AE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
   <si>
-    <t xml:space="preserve">tig</t>
+    <t>(tig) this is good</t>
   </si>
   <si>
-    <t xml:space="preserve">tib</t>
+    <t>(tib) this is bad</t>
+  </si>
+  <si>
+    <t>tig</t>
+  </si>
+  <si>
+    <t>tib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,7 +70,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -76,61 +78,314 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{670DBCAC-407B-4206-AF45-7B9780EE5BD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2905125" y="1152526"/>
+          <a:ext cx="1895475" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600" b="1"/>
+            <a:t>what I</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600" b="1" baseline="0"/>
+            <a:t> get as a file</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-CA" sz="1600" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1343025</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Arrow: Left 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9515022-3B90-47B8-88F0-F809E1129B35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1952625" y="1295400"/>
+          <a:ext cx="695325" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-CA" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1343025</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Arrow: Left 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91769173-392F-4E7F-BF4B-05C86EA6647A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1952625" y="1295400"/>
+          <a:ext cx="695325" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-CA" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{767B867F-A44B-406C-8D10-5CE532793E7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2971800" y="3657600"/>
+          <a:ext cx="2124075" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600" b="1"/>
+            <a:t>what I</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600" b="1" baseline="0"/>
+            <a:t> want as result</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-CA" sz="1600" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -165,55 +420,153 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -221,24 +574,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -251,7 +613,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -261,13 +629,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -275,6 +645,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -282,196 +653,197 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F755F5D-62E8-445F-9D39-4629FDDB725C}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:B26"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.29"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>3</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>4</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>5</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>6</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>7</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>8</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>9</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>10</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
+      <c r="B26" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>